--- a/01_INPUTS/Planes AASS/sincargosagosto.xlsx
+++ b/01_INPUTS/Planes AASS/sincargosagosto.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\Planes AASS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4048BCC3-2665-49DB-BB7D-E6E25628B1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE46B87-7065-40C3-896B-080072496E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8398F70B-36A8-4A9F-A50B-4A31C9FEDDC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8398F70B-36A8-4A9F-A50B-4A31C9FEDDC3}"/>
   </bookViews>
   <sheets>
     <sheet name="plan frío" sheetId="1" r:id="rId1"/>
     <sheet name="Planes AASS" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Planes AASS'!$B$1:$G$32</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -454,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -477,9 +480,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -487,217 +487,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1676,43 +1466,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11">
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
     <cfRule type="duplicateValues" dxfId="16" priority="16"/>
@@ -2034,7 +1824,7 @@
       <c r="I11" s="6">
         <v>10</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2106,7 +1896,7 @@
       <c r="I14" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2421,6 +2211,7 @@
       <c r="F32" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="B1:G32" xr:uid="{BE5B0672-9B1D-4469-8532-36560150BC3A}"/>
   <conditionalFormatting sqref="B2:B31">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
